--- a/MavenBook/src/test/resources/ReceiptData.xlsx
+++ b/MavenBook/src/test/resources/ReceiptData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Customer Name</t>
   </si>
@@ -49,19 +49,16 @@
     <t>25326</t>
   </si>
   <si>
-    <t>JM Traders</t>
-  </si>
-  <si>
     <t>SI45</t>
   </si>
   <si>
     <t>Bank Charges</t>
   </si>
   <si>
-    <t>SBI</t>
-  </si>
-  <si>
     <t>Bank</t>
+  </si>
+  <si>
+    <t>Deepak T</t>
   </si>
 </sst>
 </file>
@@ -483,7 +480,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H1" s="9" t="s">
         <v>6</v>
@@ -497,26 +494,24 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="F2" s="5"/>
       <c r="G2" s="11">
         <v>50</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>8</v>

--- a/MavenBook/src/test/resources/ReceiptData.xlsx
+++ b/MavenBook/src/test/resources/ReceiptData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>Customer Name</t>
   </si>
@@ -43,22 +43,46 @@
     <t>Test</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>25326</t>
-  </si>
-  <si>
-    <t>SI45</t>
-  </si>
-  <si>
     <t>Bank Charges</t>
   </si>
   <si>
-    <t>Bank</t>
-  </si>
-  <si>
-    <t>Deepak T</t>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>800</t>
+  </si>
+  <si>
+    <t>Joyal</t>
+  </si>
+  <si>
+    <t>130826-1</t>
+  </si>
+  <si>
+    <t>130826-2</t>
+  </si>
+  <si>
+    <t>130826-3</t>
+  </si>
+  <si>
+    <t>130826-4</t>
+  </si>
+  <si>
+    <t>SI233</t>
+  </si>
+  <si>
+    <t>SI225</t>
+  </si>
+  <si>
+    <t>SI226</t>
+  </si>
+  <si>
+    <t>SI206</t>
   </si>
 </sst>
 </file>
@@ -133,12 +157,14 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -444,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" style="2" customWidth="1"/>
@@ -467,30 +493,30 @@
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -498,71 +524,116 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>13</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F2" s="5"/>
-      <c r="G2" s="11">
-        <v>50</v>
-      </c>
+      <c r="G2" s="10"/>
       <c r="H2" s="6" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>8</v>
       </c>
       <c r="J2" s="6"/>
-      <c r="K2" s="10"/>
+      <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B3" s="7"/>
-      <c r="C3" s="6"/>
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
+      <c r="E3" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="F3" s="5"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>8</v>
+      </c>
       <c r="J3" s="6"/>
-      <c r="K3" s="10"/>
+      <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G4" s="2"/>
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="6"/>
+      <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" s="6"/>
+      <c r="K5" s="9"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="11"/>
+      <c r="C6" s="6"/>
+      <c r="E6" s="6"/>
       <c r="G6" s="2"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="11"/>
+      <c r="C7" s="6"/>
+      <c r="E7" s="6"/>
       <c r="G7" s="2"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G12" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="C4:C12" numberStoredAsText="1"/>
+    <ignoredError sqref="C8" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>